--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T11:58:08+00:00</t>
+    <t>2026-06-01T14:28:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4207,7 +4207,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>157</v>
       </c>
@@ -4226,7 +4226,7 @@
         <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>74</v>

--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-traitement-subordonne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:28:18+00:00</t>
+    <t>2026-06-01T15:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
